--- a/testing/glm-mv-reference/spss-output/mv3_berpasangan.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv3_berpasangan.xlsx
@@ -993,78 +993,78 @@
   </cellXfs>
   <cellStyles count="73">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1790153261511" xfId="1"/>
-    <cellStyle name="style1790153261551" xfId="2"/>
-    <cellStyle name="style1790153261573" xfId="3"/>
-    <cellStyle name="style1790153261600" xfId="4"/>
-    <cellStyle name="style1790153261627" xfId="5"/>
-    <cellStyle name="style1790153261654" xfId="6"/>
-    <cellStyle name="style1790153261670" xfId="7"/>
-    <cellStyle name="style1790153261697" xfId="8"/>
-    <cellStyle name="style1790153261722" xfId="9"/>
-    <cellStyle name="style1790153261745" xfId="10"/>
-    <cellStyle name="style1790153261765" xfId="11"/>
-    <cellStyle name="style1790153261794" xfId="12"/>
-    <cellStyle name="style1790153261815" xfId="13"/>
-    <cellStyle name="style1790153261840" xfId="14"/>
-    <cellStyle name="style1790153261867" xfId="15"/>
-    <cellStyle name="style1790153261883" xfId="16"/>
-    <cellStyle name="style1790153261898" xfId="17"/>
-    <cellStyle name="style1790153261923" xfId="18"/>
-    <cellStyle name="style1790153261951" xfId="19"/>
-    <cellStyle name="style1790153261975" xfId="20"/>
-    <cellStyle name="style1790153261999" xfId="21"/>
-    <cellStyle name="style1790153262022" xfId="22"/>
-    <cellStyle name="style1790153262036" xfId="23"/>
-    <cellStyle name="style1790153262059" xfId="24"/>
-    <cellStyle name="style1790153262083" xfId="25"/>
-    <cellStyle name="style1790153262106" xfId="26"/>
-    <cellStyle name="style1790153262129" xfId="27"/>
-    <cellStyle name="style1790153262153" xfId="28"/>
-    <cellStyle name="style1790153262176" xfId="29"/>
-    <cellStyle name="style1790153262199" xfId="30"/>
-    <cellStyle name="style1790153262217" xfId="31"/>
-    <cellStyle name="style1790153262241" xfId="32"/>
-    <cellStyle name="style1790153262262" xfId="33"/>
-    <cellStyle name="style1790153262280" xfId="34"/>
-    <cellStyle name="style1790153262295" xfId="35"/>
-    <cellStyle name="style1790153262311" xfId="36"/>
-    <cellStyle name="style1790153262324" xfId="37"/>
-    <cellStyle name="style1790153262339" xfId="38"/>
-    <cellStyle name="style1790153262356" xfId="39"/>
-    <cellStyle name="style1790153262376" xfId="40"/>
-    <cellStyle name="style1790153262391" xfId="41"/>
-    <cellStyle name="style1790153262411" xfId="42"/>
-    <cellStyle name="style1790153262429" xfId="43"/>
-    <cellStyle name="style1790153262442" xfId="44"/>
-    <cellStyle name="style1790153262454" xfId="45"/>
-    <cellStyle name="style1790153262471" xfId="46"/>
-    <cellStyle name="style1790153262487" xfId="47"/>
-    <cellStyle name="style1790153262503" xfId="48"/>
-    <cellStyle name="style1790153262524" xfId="49"/>
-    <cellStyle name="style1790153262541" xfId="50"/>
-    <cellStyle name="style1790153262559" xfId="51"/>
-    <cellStyle name="style1790153262581" xfId="52"/>
-    <cellStyle name="style1790153262599" xfId="53"/>
-    <cellStyle name="style1790153262621" xfId="54"/>
-    <cellStyle name="style1790153262641" xfId="55"/>
-    <cellStyle name="style1790153262658" xfId="56"/>
-    <cellStyle name="style1790153262675" xfId="57"/>
-    <cellStyle name="style1790153262687" xfId="58"/>
-    <cellStyle name="style1790153262710" xfId="59"/>
-    <cellStyle name="style1790153262726" xfId="60"/>
-    <cellStyle name="style1790153262742" xfId="61"/>
-    <cellStyle name="style1790153262757" xfId="62"/>
-    <cellStyle name="style1790153262778" xfId="63"/>
-    <cellStyle name="style1790153262789" xfId="64"/>
-    <cellStyle name="style1790153262804" xfId="65"/>
-    <cellStyle name="style1790153262821" xfId="66"/>
-    <cellStyle name="style1790153262835" xfId="67"/>
-    <cellStyle name="style1790153262841" xfId="68"/>
-    <cellStyle name="style1790153262862" xfId="69"/>
-    <cellStyle name="style1790153262877" xfId="70"/>
-    <cellStyle name="style1790153262893" xfId="71"/>
-    <cellStyle name="style1790153262904" xfId="72"/>
+    <cellStyle name="style1791027412769" xfId="1"/>
+    <cellStyle name="style1791027412833" xfId="2"/>
+    <cellStyle name="style1791027412865" xfId="3"/>
+    <cellStyle name="style1791027412897" xfId="4"/>
+    <cellStyle name="style1791027412927" xfId="5"/>
+    <cellStyle name="style1791027412958" xfId="6"/>
+    <cellStyle name="style1791027412982" xfId="7"/>
+    <cellStyle name="style1791027413014" xfId="8"/>
+    <cellStyle name="style1791027413045" xfId="9"/>
+    <cellStyle name="style1791027413072" xfId="10"/>
+    <cellStyle name="style1791027413104" xfId="11"/>
+    <cellStyle name="style1791027413125" xfId="12"/>
+    <cellStyle name="style1791027413171" xfId="13"/>
+    <cellStyle name="style1791027413204" xfId="14"/>
+    <cellStyle name="style1791027413236" xfId="15"/>
+    <cellStyle name="style1791027413253" xfId="16"/>
+    <cellStyle name="style1791027413283" xfId="17"/>
+    <cellStyle name="style1791027413305" xfId="18"/>
+    <cellStyle name="style1791027413336" xfId="19"/>
+    <cellStyle name="style1791027413367" xfId="20"/>
+    <cellStyle name="style1791027413399" xfId="21"/>
+    <cellStyle name="style1791027413426" xfId="22"/>
+    <cellStyle name="style1791027413444" xfId="23"/>
+    <cellStyle name="style1791027413473" xfId="24"/>
+    <cellStyle name="style1791027413505" xfId="25"/>
+    <cellStyle name="style1791027413531" xfId="26"/>
+    <cellStyle name="style1791027413554" xfId="27"/>
+    <cellStyle name="style1791027413583" xfId="28"/>
+    <cellStyle name="style1791027413605" xfId="29"/>
+    <cellStyle name="style1791027413639" xfId="30"/>
+    <cellStyle name="style1791027413667" xfId="31"/>
+    <cellStyle name="style1791027413696" xfId="32"/>
+    <cellStyle name="style1791027413720" xfId="33"/>
+    <cellStyle name="style1791027413743" xfId="34"/>
+    <cellStyle name="style1791027413762" xfId="35"/>
+    <cellStyle name="style1791027413784" xfId="36"/>
+    <cellStyle name="style1791027413806" xfId="37"/>
+    <cellStyle name="style1791027413821" xfId="38"/>
+    <cellStyle name="style1791027413847" xfId="39"/>
+    <cellStyle name="style1791027413874" xfId="40"/>
+    <cellStyle name="style1791027413895" xfId="41"/>
+    <cellStyle name="style1791027413919" xfId="42"/>
+    <cellStyle name="style1791027413933" xfId="43"/>
+    <cellStyle name="style1791027413957" xfId="44"/>
+    <cellStyle name="style1791027413974" xfId="45"/>
+    <cellStyle name="style1791027413991" xfId="46"/>
+    <cellStyle name="style1791027414016" xfId="47"/>
+    <cellStyle name="style1791027414028" xfId="48"/>
+    <cellStyle name="style1791027414059" xfId="49"/>
+    <cellStyle name="style1791027414079" xfId="50"/>
+    <cellStyle name="style1791027414107" xfId="51"/>
+    <cellStyle name="style1791027414132" xfId="52"/>
+    <cellStyle name="style1791027414158" xfId="53"/>
+    <cellStyle name="style1791027414190" xfId="54"/>
+    <cellStyle name="style1791027414216" xfId="55"/>
+    <cellStyle name="style1791027414232" xfId="56"/>
+    <cellStyle name="style1791027414252" xfId="57"/>
+    <cellStyle name="style1791027414274" xfId="58"/>
+    <cellStyle name="style1791027414296" xfId="59"/>
+    <cellStyle name="style1791027414315" xfId="60"/>
+    <cellStyle name="style1791027414335" xfId="61"/>
+    <cellStyle name="style1791027414345" xfId="62"/>
+    <cellStyle name="style1791027414378" xfId="63"/>
+    <cellStyle name="style1791027414391" xfId="64"/>
+    <cellStyle name="style1791027414413" xfId="65"/>
+    <cellStyle name="style1791027414434" xfId="66"/>
+    <cellStyle name="style1791027414453" xfId="67"/>
+    <cellStyle name="style1791027414472" xfId="68"/>
+    <cellStyle name="style1791027414485" xfId="69"/>
+    <cellStyle name="style1791027414507" xfId="70"/>
+    <cellStyle name="style1791027414521" xfId="71"/>
+    <cellStyle name="style1791027414534" xfId="72"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1491,7 +1491,7 @@
       <c r="B22" s="8"/>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>23-SEP-2026 15:47:41</t>
+          <t>03-OCT-2026 18:36:52</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.02</t>
+          <t>00:00:00.00</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>00:00:00.00</t>
+          <t>00:00:00.01</t>
         </is>
       </c>
     </row>

--- a/testing/glm-mv-reference/spss-output/mv3_berpasangan.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv3_berpasangan.xlsx
@@ -993,78 +993,78 @@
   </cellXfs>
   <cellStyles count="73">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1791027412769" xfId="1"/>
-    <cellStyle name="style1791027412833" xfId="2"/>
-    <cellStyle name="style1791027412865" xfId="3"/>
-    <cellStyle name="style1791027412897" xfId="4"/>
-    <cellStyle name="style1791027412927" xfId="5"/>
-    <cellStyle name="style1791027412958" xfId="6"/>
-    <cellStyle name="style1791027412982" xfId="7"/>
-    <cellStyle name="style1791027413014" xfId="8"/>
-    <cellStyle name="style1791027413045" xfId="9"/>
-    <cellStyle name="style1791027413072" xfId="10"/>
-    <cellStyle name="style1791027413104" xfId="11"/>
-    <cellStyle name="style1791027413125" xfId="12"/>
-    <cellStyle name="style1791027413171" xfId="13"/>
-    <cellStyle name="style1791027413204" xfId="14"/>
-    <cellStyle name="style1791027413236" xfId="15"/>
-    <cellStyle name="style1791027413253" xfId="16"/>
-    <cellStyle name="style1791027413283" xfId="17"/>
-    <cellStyle name="style1791027413305" xfId="18"/>
-    <cellStyle name="style1791027413336" xfId="19"/>
-    <cellStyle name="style1791027413367" xfId="20"/>
-    <cellStyle name="style1791027413399" xfId="21"/>
-    <cellStyle name="style1791027413426" xfId="22"/>
-    <cellStyle name="style1791027413444" xfId="23"/>
-    <cellStyle name="style1791027413473" xfId="24"/>
-    <cellStyle name="style1791027413505" xfId="25"/>
-    <cellStyle name="style1791027413531" xfId="26"/>
-    <cellStyle name="style1791027413554" xfId="27"/>
-    <cellStyle name="style1791027413583" xfId="28"/>
-    <cellStyle name="style1791027413605" xfId="29"/>
-    <cellStyle name="style1791027413639" xfId="30"/>
-    <cellStyle name="style1791027413667" xfId="31"/>
-    <cellStyle name="style1791027413696" xfId="32"/>
-    <cellStyle name="style1791027413720" xfId="33"/>
-    <cellStyle name="style1791027413743" xfId="34"/>
-    <cellStyle name="style1791027413762" xfId="35"/>
-    <cellStyle name="style1791027413784" xfId="36"/>
-    <cellStyle name="style1791027413806" xfId="37"/>
-    <cellStyle name="style1791027413821" xfId="38"/>
-    <cellStyle name="style1791027413847" xfId="39"/>
-    <cellStyle name="style1791027413874" xfId="40"/>
-    <cellStyle name="style1791027413895" xfId="41"/>
-    <cellStyle name="style1791027413919" xfId="42"/>
-    <cellStyle name="style1791027413933" xfId="43"/>
-    <cellStyle name="style1791027413957" xfId="44"/>
-    <cellStyle name="style1791027413974" xfId="45"/>
-    <cellStyle name="style1791027413991" xfId="46"/>
-    <cellStyle name="style1791027414016" xfId="47"/>
-    <cellStyle name="style1791027414028" xfId="48"/>
-    <cellStyle name="style1791027414059" xfId="49"/>
-    <cellStyle name="style1791027414079" xfId="50"/>
-    <cellStyle name="style1791027414107" xfId="51"/>
-    <cellStyle name="style1791027414132" xfId="52"/>
-    <cellStyle name="style1791027414158" xfId="53"/>
-    <cellStyle name="style1791027414190" xfId="54"/>
-    <cellStyle name="style1791027414216" xfId="55"/>
-    <cellStyle name="style1791027414232" xfId="56"/>
-    <cellStyle name="style1791027414252" xfId="57"/>
-    <cellStyle name="style1791027414274" xfId="58"/>
-    <cellStyle name="style1791027414296" xfId="59"/>
-    <cellStyle name="style1791027414315" xfId="60"/>
-    <cellStyle name="style1791027414335" xfId="61"/>
-    <cellStyle name="style1791027414345" xfId="62"/>
-    <cellStyle name="style1791027414378" xfId="63"/>
-    <cellStyle name="style1791027414391" xfId="64"/>
-    <cellStyle name="style1791027414413" xfId="65"/>
-    <cellStyle name="style1791027414434" xfId="66"/>
-    <cellStyle name="style1791027414453" xfId="67"/>
-    <cellStyle name="style1791027414472" xfId="68"/>
-    <cellStyle name="style1791027414485" xfId="69"/>
-    <cellStyle name="style1791027414507" xfId="70"/>
-    <cellStyle name="style1791027414521" xfId="71"/>
-    <cellStyle name="style1791027414534" xfId="72"/>
+    <cellStyle name="style1790153261511" xfId="1"/>
+    <cellStyle name="style1790153261551" xfId="2"/>
+    <cellStyle name="style1790153261573" xfId="3"/>
+    <cellStyle name="style1790153261600" xfId="4"/>
+    <cellStyle name="style1790153261627" xfId="5"/>
+    <cellStyle name="style1790153261654" xfId="6"/>
+    <cellStyle name="style1790153261670" xfId="7"/>
+    <cellStyle name="style1790153261697" xfId="8"/>
+    <cellStyle name="style1790153261722" xfId="9"/>
+    <cellStyle name="style1790153261745" xfId="10"/>
+    <cellStyle name="style1790153261765" xfId="11"/>
+    <cellStyle name="style1790153261794" xfId="12"/>
+    <cellStyle name="style1790153261815" xfId="13"/>
+    <cellStyle name="style1790153261840" xfId="14"/>
+    <cellStyle name="style1790153261867" xfId="15"/>
+    <cellStyle name="style1790153261883" xfId="16"/>
+    <cellStyle name="style1790153261898" xfId="17"/>
+    <cellStyle name="style1790153261923" xfId="18"/>
+    <cellStyle name="style1790153261951" xfId="19"/>
+    <cellStyle name="style1790153261975" xfId="20"/>
+    <cellStyle name="style1790153261999" xfId="21"/>
+    <cellStyle name="style1790153262022" xfId="22"/>
+    <cellStyle name="style1790153262036" xfId="23"/>
+    <cellStyle name="style1790153262059" xfId="24"/>
+    <cellStyle name="style1790153262083" xfId="25"/>
+    <cellStyle name="style1790153262106" xfId="26"/>
+    <cellStyle name="style1790153262129" xfId="27"/>
+    <cellStyle name="style1790153262153" xfId="28"/>
+    <cellStyle name="style1790153262176" xfId="29"/>
+    <cellStyle name="style1790153262199" xfId="30"/>
+    <cellStyle name="style1790153262217" xfId="31"/>
+    <cellStyle name="style1790153262241" xfId="32"/>
+    <cellStyle name="style1790153262262" xfId="33"/>
+    <cellStyle name="style1790153262280" xfId="34"/>
+    <cellStyle name="style1790153262295" xfId="35"/>
+    <cellStyle name="style1790153262311" xfId="36"/>
+    <cellStyle name="style1790153262324" xfId="37"/>
+    <cellStyle name="style1790153262339" xfId="38"/>
+    <cellStyle name="style1790153262356" xfId="39"/>
+    <cellStyle name="style1790153262376" xfId="40"/>
+    <cellStyle name="style1790153262391" xfId="41"/>
+    <cellStyle name="style1790153262411" xfId="42"/>
+    <cellStyle name="style1790153262429" xfId="43"/>
+    <cellStyle name="style1790153262442" xfId="44"/>
+    <cellStyle name="style1790153262454" xfId="45"/>
+    <cellStyle name="style1790153262471" xfId="46"/>
+    <cellStyle name="style1790153262487" xfId="47"/>
+    <cellStyle name="style1790153262503" xfId="48"/>
+    <cellStyle name="style1790153262524" xfId="49"/>
+    <cellStyle name="style1790153262541" xfId="50"/>
+    <cellStyle name="style1790153262559" xfId="51"/>
+    <cellStyle name="style1790153262581" xfId="52"/>
+    <cellStyle name="style1790153262599" xfId="53"/>
+    <cellStyle name="style1790153262621" xfId="54"/>
+    <cellStyle name="style1790153262641" xfId="55"/>
+    <cellStyle name="style1790153262658" xfId="56"/>
+    <cellStyle name="style1790153262675" xfId="57"/>
+    <cellStyle name="style1790153262687" xfId="58"/>
+    <cellStyle name="style1790153262710" xfId="59"/>
+    <cellStyle name="style1790153262726" xfId="60"/>
+    <cellStyle name="style1790153262742" xfId="61"/>
+    <cellStyle name="style1790153262757" xfId="62"/>
+    <cellStyle name="style1790153262778" xfId="63"/>
+    <cellStyle name="style1790153262789" xfId="64"/>
+    <cellStyle name="style1790153262804" xfId="65"/>
+    <cellStyle name="style1790153262821" xfId="66"/>
+    <cellStyle name="style1790153262835" xfId="67"/>
+    <cellStyle name="style1790153262841" xfId="68"/>
+    <cellStyle name="style1790153262862" xfId="69"/>
+    <cellStyle name="style1790153262877" xfId="70"/>
+    <cellStyle name="style1790153262893" xfId="71"/>
+    <cellStyle name="style1790153262904" xfId="72"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1491,7 +1491,7 @@
       <c r="B22" s="8"/>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>03-OCT-2026 18:36:52</t>
+          <t>23-SEP-2026 15:47:41</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.00</t>
+          <t>00:00:00.02</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>00:00:00.01</t>
+          <t>00:00:00.00</t>
         </is>
       </c>
     </row>
